--- a/cleaning_forms/028_flooring_cleaning_chemical_survey--cleaning_forms.xlsx
+++ b/cleaning_forms/028_flooring_cleaning_chemical_survey--cleaning_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hardwood',_'value':_'hardwood'}</t>
+          <t>hardwood</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hardwood', 'value': 'Hardwood'}</t>
+          <t>Hardwood</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tile',_'value':_'tile'}</t>
+          <t>tile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tile', 'value': 'Tile'}</t>
+          <t>Tile</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'carpet',_'value':_'carpet'}</t>
+          <t>carpet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Carpet', 'value': 'Carpet'}</t>
+          <t>Carpet</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'all-purpose_cleaner',_'value':_'all-purpose_cleaner'}</t>
+          <t>all-purpose_cleaner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'All-purpose cleaner', 'value': 'All-purpose cleaner'}</t>
+          <t>All-purpose cleaner</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'glass_cleaner',_'value':_'glass_cleaner'}</t>
+          <t>glass_cleaner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Glass cleaner', 'value': 'Glass cleaner'}</t>
+          <t>Glass cleaner</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'soap',_'value':_'soap'}</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Soap', 'value': 'Soap'}</t>
+          <t>Soap</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied', 'value': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_satisfied',_'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Satisfied', 'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
